--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92572722514</v>
+        <v>46157.9311293081</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9311293081</v>
+        <v>46157.93180271155</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93180271155</v>
+        <v>46157.93404241229</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93404241229</v>
+        <v>46157.93722271344</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93722271344</v>
+        <v>46158.28220189166</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28220189166</v>
+        <v>46158.2969660625</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2969660625</v>
+        <v>46158.29819675734</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29819675734</v>
+        <v>46158.33391222129</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391222129</v>
+        <v>46158.36861030015</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861030015</v>
+        <v>46158.37291660379</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
